--- a/docs/0OMsoqOg9GiJ2xusVHMv/.gitbook/assets/IO - Template servizi - Servizi cimiteriali.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHMv/.gitbook/assets/IO - Template servizi - Servizi cimiteriali.xlsx
@@ -697,8 +697,8 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Se hai già pagato ignora pure questo messaggio. 
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
@@ -917,124 +917,6 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">C'è un avviso da pagare intestato a </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;nome e cognome&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> e relativo a </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;causale&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>Devi pagare:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;00,00&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> €
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>Entro il:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="ff884444"/>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t>&lt;gg/mm/aaaa&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
-      <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Se hai già provveduto a pagare l'avviso ignora questo messaggio.
-Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
-In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Titillium Web"/>
-      </rPr>
       <t xml:space="preserve">Il tuo pagamento per </t>
     </r>
     <r>
@@ -1243,7 +1125,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 </t>
     </r>
     <r>
@@ -1262,7 +1144,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve"> È possibile richiedere la domiciliazione delle rette direttamente sul tuo conto corrente. Per maggiori informazioni, [visita questo sito](URL). 
-Se hai già pagato o se hai richiesto la domiciliazione sul conto corrente, ignora pure questo messaggio. 
+Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
@@ -1525,7 +1407,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 </t>
     </r>
     <r>
@@ -1650,6 +1532,142 @@
 La richiesta è subordinata a un pagamento per la pratica per cui ti arriverà un messaggio in app con l'avviso di pagamento. 
 Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve">C'è un avviso da pagare intestato a </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;nome e cognome&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> e relativo a </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;causale&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>Devi pagare:</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;00,00&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> €
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>Entro il:</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff884444"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>&lt;gg/mm/aaaa&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve">
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="ff448844"/>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t>[Se previsto]</t>
+    </r>
+    <r>
+      <rPr>
+        <family val="2"/>
+        <sz val="10"/>
+        <rFont val="Titillium Web"/>
+      </rPr>
+      <t xml:space="preserve"> È possibile richiedere la domiciliazione delle rette direttamente sul tuo conto corrente. Per maggiori informazioni, [visita questo sito](URL). 
+Se hai già pagato o se hai richiesto la domiciliazione sul conto corrente, ignora pure questo messaggio. 
+Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
+In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
   </si>
   <si>
@@ -1823,7 +1841,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Vedi Avviso</t>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <t>Disdici richiesta</t>
@@ -2968,61 +2986,61 @@
         <v>111</v>
       </c>
       <c r="K5" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="L5" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="M5" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="M5" s="34" t="s">
+      <c r="N5" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="O5" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="O5" s="34" t="s">
+      <c r="P5" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="P5" s="34" t="s">
+      <c r="Q5" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="Q5" s="34" t="s">
+      <c r="R5" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="R5" s="34" t="s">
+      <c r="S5" s="34" t="s">
         <v>119</v>
-      </c>
-      <c r="S5" s="34" t="s">
-        <v>120</v>
       </c>
       <c r="T5" s="34" t="s">
         <v>104</v>
       </c>
       <c r="U5" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="V5" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="V5" s="34" t="s">
+      <c r="W5" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="X5" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="W5" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="X5" s="34" t="s">
+      <c r="Y5" s="34" t="s">
         <v>123</v>
-      </c>
-      <c r="Y5" s="34" t="s">
-        <v>124</v>
       </c>
       <c r="Z5" s="34" t="s">
         <v>104</v>
       </c>
       <c r="AA5" s="34" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="AB5" s="34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AC5" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AD5" s="34" t="s">
         <v>125</v>
